--- a/web/public/forms/orig/o-pumjil-daejang.xlsx
+++ b/web/public/forms/orig/o-pumjil-daejang.xlsx
@@ -592,7 +592,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
@@ -1180,7 +1180,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
         </is>
       </c>
       <c r="G1" s="17" t="inlineStr">

--- a/web/public/forms/orig/o-pumjil-daejang.xlsx
+++ b/web/public/forms/orig/o-pumjil-daejang.xlsx
@@ -8,11 +8,9 @@
   </bookViews>
   <sheets>
     <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="품질검사 대장" sheetId="1" state="visible" r:id="rId1"/>
-    <sheet xmlns:r="http://schemas.openxmlformats.org/officeDocument/2006/relationships" name="작성 예시" sheetId="2" state="visible" r:id="rId2"/>
   </sheets>
   <definedNames>
     <definedName name="_xlnm.Print_Area" localSheetId="0">'품질검사 대장'!$A$1:$M$24</definedName>
-    <definedName name="_xlnm.Print_Area" localSheetId="1">'작성 예시'!$A$1:$M$24</definedName>
   </definedNames>
   <calcPr calcId="124519" fullCalcOnLoad="1"/>
 </workbook>
@@ -147,7 +145,7 @@
   <cellStyleXfs count="1">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
   </cellStyleXfs>
-  <cellXfs count="18">
+  <cellXfs count="17">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" pivotButton="0" quotePrefix="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center"/>
@@ -194,22 +192,11 @@
     </xf>
     <xf numFmtId="0" fontId="2" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
       <alignment horizontal="left" vertical="center" wrapText="1"/>
-    </xf>
-    <xf numFmtId="0" fontId="12" fillId="0" borderId="0" applyAlignment="1" pivotButton="0" quotePrefix="0" xfId="0">
-      <alignment horizontal="right" vertical="center"/>
     </xf>
   </cellXfs>
   <cellStyles count="1">
     <cellStyle name="Normal" xfId="0" builtinId="0" hidden="0"/>
   </cellStyles>
-  <dxfs count="1">
-    <dxf>
-      <font>
-        <b val="1"/>
-        <color rgb="00DC2626"/>
-      </font>
-    </dxf>
-  </dxfs>
   <tableStyles count="0" defaultTableStyle="TableStyleMedium9" defaultPivotStyle="PivotStyleLight16"/>
   <colors>
     <indexedColors>
@@ -727,10 +714,7 @@
       <c r="M5" s="5" t="n"/>
     </row>
     <row r="6" ht="31" customHeight="1">
-      <c r="A6" s="7">
-        <f>IF(E6="","",COUNTIF(E6:E6,"?*"))</f>
-        <v/>
-      </c>
+      <c r="A6" s="7" t="n"/>
       <c r="B6" s="8" t="n"/>
       <c r="C6" s="9" t="n"/>
       <c r="D6" s="10" t="n"/>
@@ -745,10 +729,7 @@
       <c r="M6" s="12" t="n"/>
     </row>
     <row r="7" ht="31" customHeight="1">
-      <c r="A7" s="7">
-        <f>IF(E7="","",COUNTIF(E6:E7,"?*"))</f>
-        <v/>
-      </c>
+      <c r="A7" s="7" t="n"/>
       <c r="B7" s="8" t="n"/>
       <c r="C7" s="9" t="n"/>
       <c r="D7" s="10" t="n"/>
@@ -763,10 +744,7 @@
       <c r="M7" s="12" t="n"/>
     </row>
     <row r="8" ht="31" customHeight="1">
-      <c r="A8" s="7">
-        <f>IF(E8="","",COUNTIF(E6:E8,"?*"))</f>
-        <v/>
-      </c>
+      <c r="A8" s="7" t="n"/>
       <c r="B8" s="8" t="n"/>
       <c r="C8" s="9" t="n"/>
       <c r="D8" s="10" t="n"/>
@@ -781,10 +759,7 @@
       <c r="M8" s="12" t="n"/>
     </row>
     <row r="9" ht="31" customHeight="1">
-      <c r="A9" s="7">
-        <f>IF(E9="","",COUNTIF(E6:E9,"?*"))</f>
-        <v/>
-      </c>
+      <c r="A9" s="7" t="n"/>
       <c r="B9" s="8" t="n"/>
       <c r="C9" s="9" t="n"/>
       <c r="D9" s="10" t="n"/>
@@ -799,10 +774,7 @@
       <c r="M9" s="12" t="n"/>
     </row>
     <row r="10" ht="31" customHeight="1">
-      <c r="A10" s="7">
-        <f>IF(E10="","",COUNTIF(E6:E10,"?*"))</f>
-        <v/>
-      </c>
+      <c r="A10" s="7" t="n"/>
       <c r="B10" s="8" t="n"/>
       <c r="C10" s="9" t="n"/>
       <c r="D10" s="10" t="n"/>
@@ -817,10 +789,7 @@
       <c r="M10" s="12" t="n"/>
     </row>
     <row r="11" ht="31" customHeight="1">
-      <c r="A11" s="7">
-        <f>IF(E11="","",COUNTIF(E6:E11,"?*"))</f>
-        <v/>
-      </c>
+      <c r="A11" s="7" t="n"/>
       <c r="B11" s="8" t="n"/>
       <c r="C11" s="9" t="n"/>
       <c r="D11" s="10" t="n"/>
@@ -835,10 +804,7 @@
       <c r="M11" s="12" t="n"/>
     </row>
     <row r="12" ht="31" customHeight="1">
-      <c r="A12" s="7">
-        <f>IF(E12="","",COUNTIF(E6:E12,"?*"))</f>
-        <v/>
-      </c>
+      <c r="A12" s="7" t="n"/>
       <c r="B12" s="8" t="n"/>
       <c r="C12" s="9" t="n"/>
       <c r="D12" s="10" t="n"/>
@@ -853,10 +819,7 @@
       <c r="M12" s="12" t="n"/>
     </row>
     <row r="13" ht="31" customHeight="1">
-      <c r="A13" s="7">
-        <f>IF(E13="","",COUNTIF(E6:E13,"?*"))</f>
-        <v/>
-      </c>
+      <c r="A13" s="7" t="n"/>
       <c r="B13" s="8" t="n"/>
       <c r="C13" s="9" t="n"/>
       <c r="D13" s="10" t="n"/>
@@ -871,10 +834,7 @@
       <c r="M13" s="12" t="n"/>
     </row>
     <row r="14" ht="31" customHeight="1">
-      <c r="A14" s="7">
-        <f>IF(E14="","",COUNTIF(E6:E14,"?*"))</f>
-        <v/>
-      </c>
+      <c r="A14" s="7" t="n"/>
       <c r="B14" s="8" t="n"/>
       <c r="C14" s="9" t="n"/>
       <c r="D14" s="10" t="n"/>
@@ -889,10 +849,7 @@
       <c r="M14" s="12" t="n"/>
     </row>
     <row r="15" ht="31" customHeight="1">
-      <c r="A15" s="7">
-        <f>IF(E15="","",COUNTIF(E6:E15,"?*"))</f>
-        <v/>
-      </c>
+      <c r="A15" s="7" t="n"/>
       <c r="B15" s="8" t="n"/>
       <c r="C15" s="9" t="n"/>
       <c r="D15" s="10" t="n"/>
@@ -907,10 +864,7 @@
       <c r="M15" s="12" t="n"/>
     </row>
     <row r="16" ht="31" customHeight="1">
-      <c r="A16" s="7">
-        <f>IF(E16="","",COUNTIF(E6:E16,"?*"))</f>
-        <v/>
-      </c>
+      <c r="A16" s="7" t="n"/>
       <c r="B16" s="8" t="n"/>
       <c r="C16" s="9" t="n"/>
       <c r="D16" s="10" t="n"/>
@@ -925,10 +879,7 @@
       <c r="M16" s="12" t="n"/>
     </row>
     <row r="17" ht="31" customHeight="1">
-      <c r="A17" s="7">
-        <f>IF(E17="","",COUNTIF(E6:E17,"?*"))</f>
-        <v/>
-      </c>
+      <c r="A17" s="7" t="n"/>
       <c r="B17" s="8" t="n"/>
       <c r="C17" s="9" t="n"/>
       <c r="D17" s="10" t="n"/>
@@ -943,10 +894,7 @@
       <c r="M17" s="12" t="n"/>
     </row>
     <row r="18" ht="31" customHeight="1">
-      <c r="A18" s="7">
-        <f>IF(E18="","",COUNTIF(E6:E18,"?*"))</f>
-        <v/>
-      </c>
+      <c r="A18" s="7" t="n"/>
       <c r="B18" s="8" t="n"/>
       <c r="C18" s="9" t="n"/>
       <c r="D18" s="10" t="n"/>
@@ -961,10 +909,7 @@
       <c r="M18" s="12" t="n"/>
     </row>
     <row r="19" ht="31" customHeight="1">
-      <c r="A19" s="7">
-        <f>IF(E19="","",COUNTIF(E6:E19,"?*"))</f>
-        <v/>
-      </c>
+      <c r="A19" s="7" t="n"/>
       <c r="B19" s="8" t="n"/>
       <c r="C19" s="9" t="n"/>
       <c r="D19" s="10" t="n"/>
@@ -979,10 +924,7 @@
       <c r="M19" s="12" t="n"/>
     </row>
     <row r="20" ht="31" customHeight="1">
-      <c r="A20" s="7">
-        <f>IF(E20="","",COUNTIF(E6:E20,"?*"))</f>
-        <v/>
-      </c>
+      <c r="A20" s="7" t="n"/>
       <c r="B20" s="8" t="n"/>
       <c r="C20" s="9" t="n"/>
       <c r="D20" s="10" t="n"/>
@@ -997,10 +939,7 @@
       <c r="M20" s="12" t="n"/>
     </row>
     <row r="21" ht="31" customHeight="1">
-      <c r="A21" s="7">
-        <f>IF(E21="","",COUNTIF(E6:E21,"?*"))</f>
-        <v/>
-      </c>
+      <c r="A21" s="7" t="n"/>
       <c r="B21" s="8" t="n"/>
       <c r="C21" s="9" t="n"/>
       <c r="D21" s="10" t="n"/>
@@ -1015,10 +954,7 @@
       <c r="M21" s="12" t="n"/>
     </row>
     <row r="22" ht="31" customHeight="1">
-      <c r="A22" s="7">
-        <f>IF(E22="","",COUNTIF(E6:E22,"?*"))</f>
-        <v/>
-      </c>
+      <c r="A22" s="7" t="n"/>
       <c r="B22" s="8" t="n"/>
       <c r="C22" s="9" t="n"/>
       <c r="D22" s="10" t="n"/>
@@ -1033,10 +969,7 @@
       <c r="M22" s="12" t="n"/>
     </row>
     <row r="23" ht="31" customHeight="1">
-      <c r="A23" s="7">
-        <f>IF(E23="","",COUNTIF(E6:E23,"?*"))</f>
-        <v/>
-      </c>
+      <c r="A23" s="7" t="n"/>
       <c r="B23" s="8" t="n"/>
       <c r="C23" s="9" t="n"/>
       <c r="D23" s="10" t="n"/>
@@ -1067,10 +1000,7 @@
       <c r="B26" s="5" t="n"/>
       <c r="C26" s="5" t="n"/>
       <c r="D26" s="5" t="n"/>
-      <c r="E26" s="15">
-        <f>IF(COUNTIF(E6:E23,"?*")=0,"","시험ㆍ검사 "&amp;COUNTIF(E6:E23,"?*")&amp;"건 · 합격 "&amp;COUNTIF(H6:H23,"합격")&amp;" · 불합격 "&amp;COUNTIF(H6:H23,"불합격")&amp;IF(COUNTIF(E6:E23,"?*")-COUNTIF(H6:H23,"합격")-COUNTIF(H6:H23,"불합격")&gt;0," · 판정 안 적음 "&amp;(COUNTIF(E6:E23,"?*")-COUNTIF(H6:H23,"합격")-COUNTIF(H6:H23,"불합격")),""))</f>
-        <v/>
-      </c>
+      <c r="E26" s="15" t="n"/>
       <c r="F26" s="5" t="n"/>
       <c r="G26" s="5" t="n"/>
       <c r="H26" s="5" t="n"/>
@@ -1080,6 +1010,7 @@
       <c r="L26" s="5" t="n"/>
       <c r="M26" s="5" t="n"/>
     </row>
+    <row r="27"/>
     <row r="28" ht="19.5" customHeight="1">
       <c r="A28" s="16" t="inlineStr">
         <is>
@@ -1133,871 +1064,6 @@
     <mergeCell ref="K4:L4"/>
     <mergeCell ref="A2:M2"/>
   </mergeCells>
-  <conditionalFormatting sqref="H6:H23">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>H6="불합격"</formula>
-    </cfRule>
-  </conditionalFormatting>
-  <dataValidations count="2">
-    <dataValidation sqref="C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
-      <formula1>"시험,검사"</formula1>
-    </dataValidation>
-    <dataValidation sqref="H6 H7 H8 H9 H10 H11 H12 H13 H14 H15 H16 H17 H18 H19 H20 H21 H22 H23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
-      <formula1>"합격,불합격"</formula1>
-    </dataValidation>
-  </dataValidations>
-  <printOptions horizontalCentered="1"/>
-  <pageMargins left="0.4" right="0.35" top="0.45" bottom="0.45" header="0.2" footer="0.2"/>
-  <pageSetup orientation="portrait" paperSize="9" fitToHeight="1" fitToWidth="1"/>
-</worksheet>
-</file>
-
-<file path=xl/worksheets/sheet2.xml><?xml version="1.0" encoding="utf-8"?>
-<worksheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main">
-  <sheetPr>
-    <tabColor rgb="00F59E0B"/>
-    <outlinePr summaryBelow="1" summaryRight="1"/>
-    <pageSetUpPr fitToPage="1"/>
-  </sheetPr>
-  <dimension ref="A1:M28"/>
-  <sheetFormatPr baseColWidth="8" defaultRowHeight="15"/>
-  <cols>
-    <col width="5.6" customWidth="1" min="1" max="1"/>
-    <col width="9.199999999999999" customWidth="1" min="2" max="2"/>
-    <col width="6.4" customWidth="1" min="3" max="3"/>
-    <col width="8.4" customWidth="1" min="4" max="4"/>
-    <col width="11.6" customWidth="1" min="5" max="5"/>
-    <col width="10.6" customWidth="1" min="6" max="6"/>
-    <col width="9.199999999999999" customWidth="1" min="7" max="7"/>
-    <col width="6.4" customWidth="1" min="8" max="8"/>
-    <col width="6.4" customWidth="1" min="9" max="9"/>
-    <col width="5.8" customWidth="1" min="10" max="10"/>
-    <col width="6.6" customWidth="1" min="11" max="11"/>
-    <col width="5.8" customWidth="1" min="12" max="12"/>
-    <col width="8.6" customWidth="1" min="13" max="13"/>
-  </cols>
-  <sheetData>
-    <row r="1" ht="20" customHeight="1">
-      <c r="A1" s="1" t="inlineStr">
-        <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
-        </is>
-      </c>
-      <c r="G1" s="17" t="inlineStr">
-        <is>
-          <t xml:space="preserve">작성 예시 (가상의 현장)  </t>
-        </is>
-      </c>
-    </row>
-    <row r="2" ht="18" customHeight="1">
-      <c r="A2" s="3" t="inlineStr">
-        <is>
-          <t>■ 건설기술 진흥법 시행규칙 [별지 제42호서식]</t>
-        </is>
-      </c>
-    </row>
-    <row r="3" ht="46" customHeight="1">
-      <c r="A3" s="4" t="inlineStr">
-        <is>
-          <t>품질검사 대장</t>
-        </is>
-      </c>
-      <c r="B3" s="5" t="n"/>
-      <c r="C3" s="5" t="n"/>
-      <c r="D3" s="5" t="n"/>
-      <c r="E3" s="5" t="n"/>
-      <c r="F3" s="5" t="n"/>
-      <c r="G3" s="5" t="n"/>
-      <c r="H3" s="5" t="n"/>
-      <c r="I3" s="5" t="n"/>
-      <c r="J3" s="5" t="n"/>
-      <c r="K3" s="5" t="n"/>
-      <c r="L3" s="5" t="n"/>
-      <c r="M3" s="5" t="n"/>
-    </row>
-    <row r="4" ht="30" customHeight="1">
-      <c r="A4" s="6" t="inlineStr">
-        <is>
-          <t>일련
-번호</t>
-        </is>
-      </c>
-      <c r="B4" s="6" t="inlineStr">
-        <is>
-          <t>연월일</t>
-        </is>
-      </c>
-      <c r="C4" s="6" t="inlineStr">
-        <is>
-          <t>시험ㆍ
-검사
-구분</t>
-        </is>
-      </c>
-      <c r="D4" s="6" t="inlineStr">
-        <is>
-          <t>재료</t>
-        </is>
-      </c>
-      <c r="E4" s="6" t="inlineStr">
-        <is>
-          <t>시험ㆍ검사
-종목</t>
-        </is>
-      </c>
-      <c r="F4" s="6" t="inlineStr">
-        <is>
-          <t>시험
-기준</t>
-        </is>
-      </c>
-      <c r="G4" s="6" t="inlineStr">
-        <is>
-          <t>시험
-결과</t>
-        </is>
-      </c>
-      <c r="H4" s="6" t="inlineStr">
-        <is>
-          <t>시험
-결과
-판정</t>
-        </is>
-      </c>
-      <c r="I4" s="6" t="inlineStr">
-        <is>
-          <t>시험ㆍ검사자</t>
-        </is>
-      </c>
-      <c r="J4" s="5" t="n"/>
-      <c r="K4" s="6" t="inlineStr">
-        <is>
-          <t>건설사업관리
-기술자 확인</t>
-        </is>
-      </c>
-      <c r="L4" s="5" t="n"/>
-      <c r="M4" s="6" t="inlineStr">
-        <is>
-          <t>비고</t>
-        </is>
-      </c>
-    </row>
-    <row r="5" ht="20" customHeight="1">
-      <c r="A5" s="5" t="n"/>
-      <c r="B5" s="5" t="n"/>
-      <c r="C5" s="5" t="n"/>
-      <c r="D5" s="5" t="n"/>
-      <c r="E5" s="5" t="n"/>
-      <c r="F5" s="5" t="n"/>
-      <c r="G5" s="5" t="n"/>
-      <c r="H5" s="5" t="n"/>
-      <c r="I5" s="6" t="inlineStr">
-        <is>
-          <t>성명</t>
-        </is>
-      </c>
-      <c r="J5" s="6" t="inlineStr">
-        <is>
-          <t>서명</t>
-        </is>
-      </c>
-      <c r="K5" s="6" t="inlineStr">
-        <is>
-          <t>성명</t>
-        </is>
-      </c>
-      <c r="L5" s="6" t="inlineStr">
-        <is>
-          <t>서명</t>
-        </is>
-      </c>
-      <c r="M5" s="5" t="n"/>
-    </row>
-    <row r="6" ht="31" customHeight="1">
-      <c r="A6" s="7">
-        <f>IF(E6="","",COUNTIF(E6:E6,"?*"))</f>
-        <v/>
-      </c>
-      <c r="B6" s="8" t="n">
-        <v>46120</v>
-      </c>
-      <c r="C6" s="9" t="inlineStr">
-        <is>
-          <t>시험</t>
-        </is>
-      </c>
-      <c r="D6" s="10" t="inlineStr">
-        <is>
-          <t>레미콘
-25-24-150</t>
-        </is>
-      </c>
-      <c r="E6" s="9" t="inlineStr">
-        <is>
-          <t>슬럼프</t>
-        </is>
-      </c>
-      <c r="F6" s="10" t="inlineStr">
-        <is>
-          <t>150±25mm</t>
-        </is>
-      </c>
-      <c r="G6" s="10" t="inlineStr">
-        <is>
-          <t>155mm</t>
-        </is>
-      </c>
-      <c r="H6" s="9" t="inlineStr">
-        <is>
-          <t>합격</t>
-        </is>
-      </c>
-      <c r="I6" s="9" t="inlineStr">
-        <is>
-          <t>김품질</t>
-        </is>
-      </c>
-      <c r="J6" s="11" t="inlineStr"/>
-      <c r="K6" s="9" t="inlineStr">
-        <is>
-          <t>박감리</t>
-        </is>
-      </c>
-      <c r="L6" s="11" t="inlineStr"/>
-      <c r="M6" s="12" t="n"/>
-    </row>
-    <row r="7" ht="31" customHeight="1">
-      <c r="A7" s="7">
-        <f>IF(E7="","",COUNTIF(E6:E7,"?*"))</f>
-        <v/>
-      </c>
-      <c r="B7" s="8" t="n">
-        <v>46120</v>
-      </c>
-      <c r="C7" s="9" t="inlineStr">
-        <is>
-          <t>시험</t>
-        </is>
-      </c>
-      <c r="D7" s="10" t="inlineStr">
-        <is>
-          <t>레미콘
-25-24-150</t>
-        </is>
-      </c>
-      <c r="E7" s="9" t="inlineStr">
-        <is>
-          <t>공기량</t>
-        </is>
-      </c>
-      <c r="F7" s="10" t="inlineStr">
-        <is>
-          <t>4.5±1.5%</t>
-        </is>
-      </c>
-      <c r="G7" s="10" t="inlineStr">
-        <is>
-          <t>4.8%</t>
-        </is>
-      </c>
-      <c r="H7" s="9" t="inlineStr">
-        <is>
-          <t>합격</t>
-        </is>
-      </c>
-      <c r="I7" s="9" t="inlineStr">
-        <is>
-          <t>김품질</t>
-        </is>
-      </c>
-      <c r="J7" s="11" t="inlineStr"/>
-      <c r="K7" s="9" t="inlineStr">
-        <is>
-          <t>박감리</t>
-        </is>
-      </c>
-      <c r="L7" s="11" t="inlineStr"/>
-      <c r="M7" s="12" t="n"/>
-    </row>
-    <row r="8" ht="31" customHeight="1">
-      <c r="A8" s="7">
-        <f>IF(E8="","",COUNTIF(E6:E8,"?*"))</f>
-        <v/>
-      </c>
-      <c r="B8" s="8" t="n">
-        <v>46120</v>
-      </c>
-      <c r="C8" s="9" t="inlineStr">
-        <is>
-          <t>시험</t>
-        </is>
-      </c>
-      <c r="D8" s="10" t="inlineStr">
-        <is>
-          <t>레미콘
-25-24-150</t>
-        </is>
-      </c>
-      <c r="E8" s="9" t="inlineStr">
-        <is>
-          <t>염화물량</t>
-        </is>
-      </c>
-      <c r="F8" s="10" t="inlineStr">
-        <is>
-          <t>0.30kg/㎥ 이하</t>
-        </is>
-      </c>
-      <c r="G8" s="10" t="inlineStr">
-        <is>
-          <t>0.042kg/㎥</t>
-        </is>
-      </c>
-      <c r="H8" s="9" t="inlineStr">
-        <is>
-          <t>합격</t>
-        </is>
-      </c>
-      <c r="I8" s="9" t="inlineStr">
-        <is>
-          <t>김품질</t>
-        </is>
-      </c>
-      <c r="J8" s="11" t="inlineStr"/>
-      <c r="K8" s="9" t="inlineStr">
-        <is>
-          <t>박감리</t>
-        </is>
-      </c>
-      <c r="L8" s="11" t="inlineStr"/>
-      <c r="M8" s="12" t="n"/>
-    </row>
-    <row r="9" ht="31" customHeight="1">
-      <c r="A9" s="7">
-        <f>IF(E9="","",COUNTIF(E6:E9,"?*"))</f>
-        <v/>
-      </c>
-      <c r="B9" s="8" t="n">
-        <v>46122</v>
-      </c>
-      <c r="C9" s="9" t="inlineStr">
-        <is>
-          <t>시험</t>
-        </is>
-      </c>
-      <c r="D9" s="10" t="inlineStr">
-        <is>
-          <t>보조기층</t>
-        </is>
-      </c>
-      <c r="E9" s="9" t="inlineStr">
-        <is>
-          <t>현장밀도
-(다짐도)</t>
-        </is>
-      </c>
-      <c r="F9" s="10" t="inlineStr">
-        <is>
-          <t>95% 이상</t>
-        </is>
-      </c>
-      <c r="G9" s="10" t="inlineStr">
-        <is>
-          <t>97.2%</t>
-        </is>
-      </c>
-      <c r="H9" s="9" t="inlineStr">
-        <is>
-          <t>합격</t>
-        </is>
-      </c>
-      <c r="I9" s="9" t="inlineStr">
-        <is>
-          <t>김품질</t>
-        </is>
-      </c>
-      <c r="J9" s="11" t="inlineStr"/>
-      <c r="K9" s="9" t="inlineStr">
-        <is>
-          <t>박감리</t>
-        </is>
-      </c>
-      <c r="L9" s="11" t="inlineStr"/>
-      <c r="M9" s="12" t="n"/>
-    </row>
-    <row r="10" ht="31" customHeight="1">
-      <c r="A10" s="7">
-        <f>IF(E10="","",COUNTIF(E6:E10,"?*"))</f>
-        <v/>
-      </c>
-      <c r="B10" s="8" t="n">
-        <v>46127</v>
-      </c>
-      <c r="C10" s="9" t="inlineStr">
-        <is>
-          <t>검사</t>
-        </is>
-      </c>
-      <c r="D10" s="10" t="inlineStr">
-        <is>
-          <t>철근 SD400
-D19</t>
-        </is>
-      </c>
-      <c r="E10" s="9" t="inlineStr">
-        <is>
-          <t>인장강도</t>
-        </is>
-      </c>
-      <c r="F10" s="10" t="inlineStr">
-        <is>
-          <t>560MPa 이상</t>
-        </is>
-      </c>
-      <c r="G10" s="10" t="inlineStr">
-        <is>
-          <t>598MPa</t>
-        </is>
-      </c>
-      <c r="H10" s="9" t="inlineStr">
-        <is>
-          <t>합격</t>
-        </is>
-      </c>
-      <c r="I10" s="9" t="inlineStr">
-        <is>
-          <t>김품질</t>
-        </is>
-      </c>
-      <c r="J10" s="11" t="inlineStr"/>
-      <c r="K10" s="9" t="inlineStr">
-        <is>
-          <t>박감리</t>
-        </is>
-      </c>
-      <c r="L10" s="11" t="inlineStr"/>
-      <c r="M10" s="12" t="inlineStr">
-        <is>
-          <t>외부 의뢰</t>
-        </is>
-      </c>
-    </row>
-    <row r="11" ht="31" customHeight="1">
-      <c r="A11" s="7">
-        <f>IF(E11="","",COUNTIF(E6:E11,"?*"))</f>
-        <v/>
-      </c>
-      <c r="B11" s="8" t="n">
-        <v>46148</v>
-      </c>
-      <c r="C11" s="9" t="inlineStr">
-        <is>
-          <t>시험</t>
-        </is>
-      </c>
-      <c r="D11" s="10" t="inlineStr">
-        <is>
-          <t>레미콘
-25-24-150</t>
-        </is>
-      </c>
-      <c r="E11" s="9" t="inlineStr">
-        <is>
-          <t>압축강도(28일)</t>
-        </is>
-      </c>
-      <c r="F11" s="10" t="inlineStr">
-        <is>
-          <t>24MPa 이상</t>
-        </is>
-      </c>
-      <c r="G11" s="10" t="inlineStr">
-        <is>
-          <t>26.1MPa</t>
-        </is>
-      </c>
-      <c r="H11" s="9" t="inlineStr">
-        <is>
-          <t>합격</t>
-        </is>
-      </c>
-      <c r="I11" s="9" t="inlineStr">
-        <is>
-          <t>김품질</t>
-        </is>
-      </c>
-      <c r="J11" s="11" t="inlineStr"/>
-      <c r="K11" s="9" t="inlineStr">
-        <is>
-          <t>박감리</t>
-        </is>
-      </c>
-      <c r="L11" s="11" t="inlineStr"/>
-      <c r="M11" s="12" t="inlineStr">
-        <is>
-          <t>4/8 타설분</t>
-        </is>
-      </c>
-    </row>
-    <row r="12" ht="31" customHeight="1">
-      <c r="A12" s="7">
-        <f>IF(E12="","",COUNTIF(E6:E12,"?*"))</f>
-        <v/>
-      </c>
-      <c r="B12" s="8" t="n">
-        <v>46150</v>
-      </c>
-      <c r="C12" s="9" t="inlineStr">
-        <is>
-          <t>시험</t>
-        </is>
-      </c>
-      <c r="D12" s="10" t="inlineStr">
-        <is>
-          <t>성토(노체)</t>
-        </is>
-      </c>
-      <c r="E12" s="9" t="inlineStr">
-        <is>
-          <t>현장밀도
-(다짐도)</t>
-        </is>
-      </c>
-      <c r="F12" s="10" t="inlineStr">
-        <is>
-          <t>90% 이상</t>
-        </is>
-      </c>
-      <c r="G12" s="10" t="inlineStr">
-        <is>
-          <t>88.5%</t>
-        </is>
-      </c>
-      <c r="H12" s="9" t="inlineStr">
-        <is>
-          <t>불합격</t>
-        </is>
-      </c>
-      <c r="I12" s="9" t="inlineStr">
-        <is>
-          <t>김품질</t>
-        </is>
-      </c>
-      <c r="J12" s="11" t="inlineStr"/>
-      <c r="K12" s="9" t="inlineStr">
-        <is>
-          <t>박감리</t>
-        </is>
-      </c>
-      <c r="L12" s="11" t="inlineStr"/>
-      <c r="M12" s="12" t="inlineStr">
-        <is>
-          <t>재다짐 후 재시험</t>
-        </is>
-      </c>
-    </row>
-    <row r="13" ht="31" customHeight="1">
-      <c r="A13" s="7">
-        <f>IF(E13="","",COUNTIF(E6:E13,"?*"))</f>
-        <v/>
-      </c>
-      <c r="B13" s="8" t="n">
-        <v>46151</v>
-      </c>
-      <c r="C13" s="9" t="inlineStr">
-        <is>
-          <t>시험</t>
-        </is>
-      </c>
-      <c r="D13" s="10" t="inlineStr">
-        <is>
-          <t>성토(노체)</t>
-        </is>
-      </c>
-      <c r="E13" s="9" t="inlineStr">
-        <is>
-          <t>현장밀도
-(다짐도)</t>
-        </is>
-      </c>
-      <c r="F13" s="10" t="inlineStr">
-        <is>
-          <t>90% 이상</t>
-        </is>
-      </c>
-      <c r="G13" s="10" t="inlineStr">
-        <is>
-          <t>92.1%</t>
-        </is>
-      </c>
-      <c r="H13" s="9" t="inlineStr">
-        <is>
-          <t>합격</t>
-        </is>
-      </c>
-      <c r="I13" s="9" t="inlineStr">
-        <is>
-          <t>김품질</t>
-        </is>
-      </c>
-      <c r="J13" s="11" t="inlineStr"/>
-      <c r="K13" s="9" t="inlineStr">
-        <is>
-          <t>박감리</t>
-        </is>
-      </c>
-      <c r="L13" s="11" t="inlineStr"/>
-      <c r="M13" s="12" t="inlineStr">
-        <is>
-          <t>5/8 재시험</t>
-        </is>
-      </c>
-    </row>
-    <row r="14" ht="31" customHeight="1">
-      <c r="A14" s="7">
-        <f>IF(E14="","",COUNTIF(E6:E14,"?*"))</f>
-        <v/>
-      </c>
-      <c r="B14" s="8" t="n"/>
-      <c r="C14" s="9" t="n"/>
-      <c r="D14" s="10" t="n"/>
-      <c r="E14" s="9" t="n"/>
-      <c r="F14" s="10" t="n"/>
-      <c r="G14" s="10" t="n"/>
-      <c r="H14" s="9" t="n"/>
-      <c r="I14" s="9" t="n"/>
-      <c r="J14" s="11" t="inlineStr"/>
-      <c r="K14" s="9" t="n"/>
-      <c r="L14" s="11" t="inlineStr"/>
-      <c r="M14" s="12" t="n"/>
-    </row>
-    <row r="15" ht="31" customHeight="1">
-      <c r="A15" s="7">
-        <f>IF(E15="","",COUNTIF(E6:E15,"?*"))</f>
-        <v/>
-      </c>
-      <c r="B15" s="8" t="n"/>
-      <c r="C15" s="9" t="n"/>
-      <c r="D15" s="10" t="n"/>
-      <c r="E15" s="9" t="n"/>
-      <c r="F15" s="10" t="n"/>
-      <c r="G15" s="10" t="n"/>
-      <c r="H15" s="9" t="n"/>
-      <c r="I15" s="9" t="n"/>
-      <c r="J15" s="11" t="inlineStr"/>
-      <c r="K15" s="9" t="n"/>
-      <c r="L15" s="11" t="inlineStr"/>
-      <c r="M15" s="12" t="n"/>
-    </row>
-    <row r="16" ht="31" customHeight="1">
-      <c r="A16" s="7">
-        <f>IF(E16="","",COUNTIF(E6:E16,"?*"))</f>
-        <v/>
-      </c>
-      <c r="B16" s="8" t="n"/>
-      <c r="C16" s="9" t="n"/>
-      <c r="D16" s="10" t="n"/>
-      <c r="E16" s="9" t="n"/>
-      <c r="F16" s="10" t="n"/>
-      <c r="G16" s="10" t="n"/>
-      <c r="H16" s="9" t="n"/>
-      <c r="I16" s="9" t="n"/>
-      <c r="J16" s="11" t="inlineStr"/>
-      <c r="K16" s="9" t="n"/>
-      <c r="L16" s="11" t="inlineStr"/>
-      <c r="M16" s="12" t="n"/>
-    </row>
-    <row r="17" ht="31" customHeight="1">
-      <c r="A17" s="7">
-        <f>IF(E17="","",COUNTIF(E6:E17,"?*"))</f>
-        <v/>
-      </c>
-      <c r="B17" s="8" t="n"/>
-      <c r="C17" s="9" t="n"/>
-      <c r="D17" s="10" t="n"/>
-      <c r="E17" s="9" t="n"/>
-      <c r="F17" s="10" t="n"/>
-      <c r="G17" s="10" t="n"/>
-      <c r="H17" s="9" t="n"/>
-      <c r="I17" s="9" t="n"/>
-      <c r="J17" s="11" t="inlineStr"/>
-      <c r="K17" s="9" t="n"/>
-      <c r="L17" s="11" t="inlineStr"/>
-      <c r="M17" s="12" t="n"/>
-    </row>
-    <row r="18" ht="31" customHeight="1">
-      <c r="A18" s="7">
-        <f>IF(E18="","",COUNTIF(E6:E18,"?*"))</f>
-        <v/>
-      </c>
-      <c r="B18" s="8" t="n"/>
-      <c r="C18" s="9" t="n"/>
-      <c r="D18" s="10" t="n"/>
-      <c r="E18" s="9" t="n"/>
-      <c r="F18" s="10" t="n"/>
-      <c r="G18" s="10" t="n"/>
-      <c r="H18" s="9" t="n"/>
-      <c r="I18" s="9" t="n"/>
-      <c r="J18" s="11" t="inlineStr"/>
-      <c r="K18" s="9" t="n"/>
-      <c r="L18" s="11" t="inlineStr"/>
-      <c r="M18" s="12" t="n"/>
-    </row>
-    <row r="19" ht="31" customHeight="1">
-      <c r="A19" s="7">
-        <f>IF(E19="","",COUNTIF(E6:E19,"?*"))</f>
-        <v/>
-      </c>
-      <c r="B19" s="8" t="n"/>
-      <c r="C19" s="9" t="n"/>
-      <c r="D19" s="10" t="n"/>
-      <c r="E19" s="9" t="n"/>
-      <c r="F19" s="10" t="n"/>
-      <c r="G19" s="10" t="n"/>
-      <c r="H19" s="9" t="n"/>
-      <c r="I19" s="9" t="n"/>
-      <c r="J19" s="11" t="inlineStr"/>
-      <c r="K19" s="9" t="n"/>
-      <c r="L19" s="11" t="inlineStr"/>
-      <c r="M19" s="12" t="n"/>
-    </row>
-    <row r="20" ht="31" customHeight="1">
-      <c r="A20" s="7">
-        <f>IF(E20="","",COUNTIF(E6:E20,"?*"))</f>
-        <v/>
-      </c>
-      <c r="B20" s="8" t="n"/>
-      <c r="C20" s="9" t="n"/>
-      <c r="D20" s="10" t="n"/>
-      <c r="E20" s="9" t="n"/>
-      <c r="F20" s="10" t="n"/>
-      <c r="G20" s="10" t="n"/>
-      <c r="H20" s="9" t="n"/>
-      <c r="I20" s="9" t="n"/>
-      <c r="J20" s="11" t="inlineStr"/>
-      <c r="K20" s="9" t="n"/>
-      <c r="L20" s="11" t="inlineStr"/>
-      <c r="M20" s="12" t="n"/>
-    </row>
-    <row r="21" ht="31" customHeight="1">
-      <c r="A21" s="7">
-        <f>IF(E21="","",COUNTIF(E6:E21,"?*"))</f>
-        <v/>
-      </c>
-      <c r="B21" s="8" t="n"/>
-      <c r="C21" s="9" t="n"/>
-      <c r="D21" s="10" t="n"/>
-      <c r="E21" s="9" t="n"/>
-      <c r="F21" s="10" t="n"/>
-      <c r="G21" s="10" t="n"/>
-      <c r="H21" s="9" t="n"/>
-      <c r="I21" s="9" t="n"/>
-      <c r="J21" s="11" t="inlineStr"/>
-      <c r="K21" s="9" t="n"/>
-      <c r="L21" s="11" t="inlineStr"/>
-      <c r="M21" s="12" t="n"/>
-    </row>
-    <row r="22" ht="31" customHeight="1">
-      <c r="A22" s="7">
-        <f>IF(E22="","",COUNTIF(E6:E22,"?*"))</f>
-        <v/>
-      </c>
-      <c r="B22" s="8" t="n"/>
-      <c r="C22" s="9" t="n"/>
-      <c r="D22" s="10" t="n"/>
-      <c r="E22" s="9" t="n"/>
-      <c r="F22" s="10" t="n"/>
-      <c r="G22" s="10" t="n"/>
-      <c r="H22" s="9" t="n"/>
-      <c r="I22" s="9" t="n"/>
-      <c r="J22" s="11" t="inlineStr"/>
-      <c r="K22" s="9" t="n"/>
-      <c r="L22" s="11" t="inlineStr"/>
-      <c r="M22" s="12" t="n"/>
-    </row>
-    <row r="23" ht="31" customHeight="1">
-      <c r="A23" s="7">
-        <f>IF(E23="","",COUNTIF(E6:E23,"?*"))</f>
-        <v/>
-      </c>
-      <c r="B23" s="8" t="n"/>
-      <c r="C23" s="9" t="n"/>
-      <c r="D23" s="10" t="n"/>
-      <c r="E23" s="9" t="n"/>
-      <c r="F23" s="10" t="n"/>
-      <c r="G23" s="10" t="n"/>
-      <c r="H23" s="9" t="n"/>
-      <c r="I23" s="9" t="n"/>
-      <c r="J23" s="11" t="inlineStr"/>
-      <c r="K23" s="9" t="n"/>
-      <c r="L23" s="11" t="inlineStr"/>
-      <c r="M23" s="12" t="n"/>
-    </row>
-    <row r="24" ht="16" customHeight="1">
-      <c r="A24" s="13" t="inlineStr">
-        <is>
-          <t>210㎜×297㎜[백상지 80g/㎡(재활용품)]</t>
-        </is>
-      </c>
-    </row>
-    <row r="25" ht="8" customHeight="1"/>
-    <row r="26" ht="22" customHeight="1">
-      <c r="A26" s="14" t="inlineStr">
-        <is>
-          <t>집계 (인쇄 안 됨)</t>
-        </is>
-      </c>
-      <c r="B26" s="5" t="n"/>
-      <c r="C26" s="5" t="n"/>
-      <c r="D26" s="5" t="n"/>
-      <c r="E26" s="15">
-        <f>IF(COUNTIF(E6:E23,"?*")=0,"","시험ㆍ검사 "&amp;COUNTIF(E6:E23,"?*")&amp;"건 · 합격 "&amp;COUNTIF(H6:H23,"합격")&amp;" · 불합격 "&amp;COUNTIF(H6:H23,"불합격")&amp;IF(COUNTIF(E6:E23,"?*")-COUNTIF(H6:H23,"합격")-COUNTIF(H6:H23,"불합격")&gt;0," · 판정 안 적음 "&amp;(COUNTIF(E6:E23,"?*")-COUNTIF(H6:H23,"합격")-COUNTIF(H6:H23,"불합격")),""))</f>
-        <v/>
-      </c>
-      <c r="F26" s="5" t="n"/>
-      <c r="G26" s="5" t="n"/>
-      <c r="H26" s="5" t="n"/>
-      <c r="I26" s="5" t="n"/>
-      <c r="J26" s="5" t="n"/>
-      <c r="K26" s="5" t="n"/>
-      <c r="L26" s="5" t="n"/>
-      <c r="M26" s="5" t="n"/>
-    </row>
-    <row r="28" ht="19.5" customHeight="1">
-      <c r="A28" s="16" t="inlineStr">
-        <is>
-          <t>이 시트는 작성 예시입니다(가상의 공사 · 사람).</t>
-        </is>
-      </c>
-    </row>
-  </sheetData>
-  <mergeCells count="19">
-    <mergeCell ref="C4:C5"/>
-    <mergeCell ref="E4:E5"/>
-    <mergeCell ref="G1:M1"/>
-    <mergeCell ref="A28:M28"/>
-    <mergeCell ref="D4:D5"/>
-    <mergeCell ref="E26:M26"/>
-    <mergeCell ref="A24:M24"/>
-    <mergeCell ref="A4:A5"/>
-    <mergeCell ref="G4:G5"/>
-    <mergeCell ref="I4:J4"/>
-    <mergeCell ref="M4:M5"/>
-    <mergeCell ref="B4:B5"/>
-    <mergeCell ref="F4:F5"/>
-    <mergeCell ref="A1:F1"/>
-    <mergeCell ref="A26:D26"/>
-    <mergeCell ref="H4:H5"/>
-    <mergeCell ref="A3:M3"/>
-    <mergeCell ref="K4:L4"/>
-    <mergeCell ref="A2:M2"/>
-  </mergeCells>
-  <conditionalFormatting sqref="H6:H23">
-    <cfRule type="expression" priority="1" dxfId="0">
-      <formula>H6="불합격"</formula>
-    </cfRule>
-  </conditionalFormatting>
   <dataValidations count="2">
     <dataValidation sqref="C6 C7 C8 C9 C10 C11 C12 C13 C14 C15 C16 C17 C18 C19 C20 C21 C22 C23" showDropDown="0" showInputMessage="0" showErrorMessage="0" allowBlank="1" error="목록에서 고르세요" type="list">
       <formula1>"시험,검사"</formula1>

--- a/web/public/forms/orig/o-pumjil-daejang.xlsx
+++ b/web/public/forms/orig/o-pumjil-daejang.xlsx
@@ -579,7 +579,7 @@
     <row r="1" ht="20" customHeight="1">
       <c r="A1" s="1" t="inlineStr">
         <is>
-          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  건설 서식</t>
+          <t xml:space="preserve">  K-건설맵  |  k-conmap.com  무료 건설 서식</t>
         </is>
       </c>
       <c r="G1" s="2" t="inlineStr">
